--- a/Distribution_SAQ_20260608.xlsx
+++ b/Distribution_SAQ_20260608.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="0000703C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -84,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -107,9 +117,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,18 +542,14 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>erreur_api</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>400 Client Error: Bad Request for url: https://www.saq.com/en/store/locator/ajaxlist/context/product/id/417396?loaded=0&amp;latitude=45.5088&amp;longitude=-73.5540</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -583,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -626,6 +633,306 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>De Maisonneuve - City Councillors</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>SAQ Sélection</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>La Cité - Les Galeries du Parc</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Faubourg Sainte-Catherine</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Mont-Royal Est - Mentana</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>SAQ Express</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Mont-Royal Est - Papineau</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>SAQ Sélection</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Av. Laurier Est</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Place Longueuil</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Longueuil</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Ateliers Angus</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>SAQ Sélection</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>SAQ Sélection</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Saint-Lambert</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>15544570</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Beach Day Every Day Vodka Frozen Berries</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>L'Île-des-Soeurs</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>SAQ Sélection</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Distribution_SAQ_20260608.xlsx
+++ b/Distribution_SAQ_20260608.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,12 +46,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="0000703C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -117,10 +111,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,7 +536,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>264</v>
+        <v>402</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -563,18 +557,14 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>erreur_id</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>ID interne non trouve</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -590,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,12 +636,12 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>De Maisonneuve - City Councillors</t>
+          <t>Place D'Armes</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -660,7 +650,7 @@
         </is>
       </c>
       <c r="F2" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -676,7 +666,7 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>La Cité - Les Galeries du Parc</t>
+          <t>Complexe Desjardins</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -690,7 +680,7 @@
         </is>
       </c>
       <c r="F3" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -706,12 +696,12 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Faubourg Sainte-Catherine</t>
+          <t>Place Dupuis</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -720,7 +710,7 @@
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -736,12 +726,12 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Mont-Royal Est - Mentana</t>
+          <t>Du Village</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -750,7 +740,7 @@
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -766,7 +756,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Mont-Royal Est - Papineau</t>
+          <t>De Maisonneuve - City Councillors</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -780,7 +770,7 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -796,7 +786,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Av. Laurier Est</t>
+          <t>Halles de la Gare</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -826,7 +816,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Place Longueuil</t>
+          <t>Centre Eaton</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -836,11 +826,11 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Longueuil</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -856,12 +846,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Ateliers Angus</t>
+          <t>La Cité - Les Galeries du Parc</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -870,7 +860,7 @@
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -886,21 +876,21 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
+          <t>Griffintown</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Saint-Lambert</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -916,21 +906,321 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>L'Île-des-Soeurs</t>
+          <t>St-Laurent - Des Pins</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Place D'Armes</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Complexe Desjardins</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Place Dupuis</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>SAQ Express</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Du Village</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>De Maisonneuve - City Councillors</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
           <t>SAQ Sélection</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Montréal</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>13</v>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Halles de la Gare</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Centre Eaton</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>La Cité - Les Galeries du Parc</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Griffintown</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Mate Libre Eau Petillante</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>St-Laurent - Des Pins</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>SAQ</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Distribution_SAQ_20260608.xlsx
+++ b/Distribution_SAQ_20260608.xlsx
@@ -45,7 +45,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0000703C"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C68" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="C84" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="C116" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="C118" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C122" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="C124" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="C128" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C130" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="C132" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="C134" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="C136" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="C138" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C140" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="C142" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="C144" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="C146" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="C148" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="C150" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="C152" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="C154" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="C156" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C158" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="C160" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="C162" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="C164" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="C166" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C167" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="C168" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="C169" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C170" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="C172" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="C173" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="C174" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C175" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C176" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="C177" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="C178" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="C179" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C180" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="C181" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="C182" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="C183" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="C184" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C185" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="C186" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="C187" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="C188" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="C189" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="C190" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="C191" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="C192" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="C193" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C194" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C195" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="C196" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="C197" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="C198" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="C199" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="C200" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="C201" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="C202" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C203" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="C204" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="C205" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="C206" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="C207" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="C208" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="C209" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="C210" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="C211" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="C212" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="C213" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="C214" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="C215" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="C216" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="C217" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="C218" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="C219" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="C220" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="C221" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="C222" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="C223" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="C224" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="C225" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="C226" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D226" s="7" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="C227" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="C228" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D228" s="7" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="C229" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="C230" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D230" s="7" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="C231" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="C232" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D232" s="7" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="C233" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="C234" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D234" s="7" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="C235" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="C236" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D236" s="7" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="C237" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="C238" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="C239" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="C240" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="C241" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="C242" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D242" s="7" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="C243" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="C244" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D244" s="7" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="C245" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="C246" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D246" s="7" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="C247" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="C248" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D248" s="7" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="C249" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="C250" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D250" s="7" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="C251" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="C252" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D252" s="7" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="C253" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="C254" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D254" s="7" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="C255" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="C256" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D256" s="7" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="C257" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="C258" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D258" s="7" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="C259" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="C260" s="8" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D260" s="7" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="C261" s="5" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
